--- a/assets/data/airway-beacons-eastern-us.xlsx
+++ b/assets/data/airway-beacons-eastern-us.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20384"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r90845434\AppData\Local\Temp\fz3temp-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZhannaStandard\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2209C2F8-F057-48D9-AED7-AB30A01F2EAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{208371F7-CEA2-4C6C-AEFF-2B1DB2BCA9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="33120" windowHeight="18270" tabRatio="243" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="213" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="airway-beacons-list-eastern-u-s" sheetId="1" r:id="rId1"/>
+    <sheet name="airway-beacons-eastern-us" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'airway-beacons-list-eastern-u-s'!$A$1:$M$564</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'airway-beacons-eastern-us'!$A$1:$M$564</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -6130,9 +6130,6 @@
     <t>Destroyed, as of 11/21/2013. Reported by hrdwrkr.</t>
   </si>
   <si>
-    <t>Arrow intact, as of 1/15/2015. Reported by Chris.</t>
-  </si>
-  <si>
     <t>Beacon intact, as of 11/21/2013. Reported by Dick Merrill.</t>
   </si>
   <si>
@@ -6184,9 +6181,6 @@
     <t>Arrow at site of Atlanta-New York Airway Beacon #9</t>
   </si>
   <si>
-    <t>Arrow intact as of 6/11/2019. Reported by Catharine Graham.</t>
-  </si>
-  <si>
     <t>Site is overgrown with grass.  Personal inspection on foot by a local resident confirms the existence of an arrow.  Additionally, the foundations from the caretakers house remain in the tree area NE of the arrow.  Reported 8/7/2019 by Ray.</t>
   </si>
   <si>
@@ -6227,13 +6221,19 @@
   </si>
   <si>
     <t>Tower and light intact and operating, as of 10/24/2020. Not the original location. oval tag on the gear box  sn.  27 original location Salem,Va.  The tower was brought to CXE (Chase City, Va. Municipal Airport) in 1966 ? and had been in operation  until 5-6 years ago for lack of maintenance. Renewed interest in the airport and a change in the town management  has led to the airport being renovated into a functioning airport. About 3 years ago a microburst knocked the tower over and damaged the tower with only minor damage to the light. The tower was 48 hrs from being cut for scrap when we found out  the plans for it  and members of the town council stopped it. After looking for parts for the tower and light I discovered what  the tower was and when it was built. I  rebuilt about 40% of the tower leaving as much of the original  as possible bearing Dept. of Commercial Aviation and part numbers stamped in them.  We updated the lights to Leds but will change them back if they do not put out enough light. One interesting note the rear light has a cobalt blue lens instead of the red or green like the other ones  that I have found information on  and it still has the Fresnel lens. Reported by Monty Hightower.</t>
+  </si>
+  <si>
+    <t>Arrow intact, as of 1/15/2015. Reported by Chris. Arrow intact; seems like the state (or some other organization) is taking care of it. Reported 4/25/2026 by Garrett McDonald.</t>
+  </si>
+  <si>
+    <t>Arrow intact as of 6/11/2019. Reported by Catharine Graham.Parts of the site along Beacon Hill Road are buried or destroyed, arrow intact as of 4/25/2026. Reported by Garrett McDonald.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6759,7 +6759,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="34" applyAlignment="1">
@@ -6769,14 +6769,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7104,25 +7102,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P564"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="34.28515625" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" customWidth="1"/>
+    <col min="4" max="4" width="25.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
+    <col min="7" max="7" width="34.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7163,13 +7161,13 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1445</v>
       </c>
@@ -7207,10 +7205,10 @@
         <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1446</v>
       </c>
@@ -7251,10 +7249,10 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1447</v>
       </c>
@@ -7292,10 +7290,10 @@
         <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1448</v>
       </c>
@@ -7330,10 +7328,10 @@
         <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1449</v>
       </c>
@@ -7368,10 +7366,10 @@
         <v>36</v>
       </c>
       <c r="N6" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1450</v>
       </c>
@@ -7406,10 +7404,10 @@
         <v>36</v>
       </c>
       <c r="N7" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1451</v>
       </c>
@@ -7447,10 +7445,10 @@
         <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1452</v>
       </c>
@@ -7491,10 +7489,10 @@
         <v>36</v>
       </c>
       <c r="N9" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1453</v>
       </c>
@@ -7535,10 +7533,10 @@
         <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1454</v>
       </c>
@@ -7576,10 +7574,10 @@
         <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>1455</v>
       </c>
@@ -7617,10 +7615,10 @@
         <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>1456</v>
       </c>
@@ -7655,10 +7653,10 @@
         <v>36</v>
       </c>
       <c r="N13" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>1457</v>
       </c>
@@ -7693,10 +7691,10 @@
         <v>36</v>
       </c>
       <c r="N14" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1458</v>
       </c>
@@ -7731,10 +7729,10 @@
         <v>36</v>
       </c>
       <c r="N15" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>1459</v>
       </c>
@@ -7769,10 +7767,10 @@
         <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1460</v>
       </c>
@@ -7801,10 +7799,10 @@
         <v>19</v>
       </c>
       <c r="N17" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>1461</v>
       </c>
@@ -7845,10 +7843,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>1462</v>
       </c>
@@ -7886,10 +7884,10 @@
         <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>1463</v>
       </c>
@@ -7921,10 +7919,10 @@
         <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>1464</v>
       </c>
@@ -7962,10 +7960,10 @@
         <v>19</v>
       </c>
       <c r="N21" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>1465</v>
       </c>
@@ -8006,10 +8004,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>1466</v>
       </c>
@@ -8047,10 +8045,10 @@
         <v>19</v>
       </c>
       <c r="N23" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>1467</v>
       </c>
@@ -8088,10 +8086,10 @@
         <v>19</v>
       </c>
       <c r="N24" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>1468</v>
       </c>
@@ -8129,10 +8127,10 @@
         <v>19</v>
       </c>
       <c r="N25" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>1469</v>
       </c>
@@ -8173,10 +8171,10 @@
         <v>36</v>
       </c>
       <c r="N26" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>1470</v>
       </c>
@@ -8217,10 +8215,10 @@
         <v>36</v>
       </c>
       <c r="N27" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>1471</v>
       </c>
@@ -8255,10 +8253,10 @@
         <v>36</v>
       </c>
       <c r="N28" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>1472</v>
       </c>
@@ -8299,10 +8297,10 @@
         <v>36</v>
       </c>
       <c r="N29" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>1473</v>
       </c>
@@ -8334,10 +8332,10 @@
         <v>19</v>
       </c>
       <c r="N30" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1474</v>
       </c>
@@ -8369,10 +8367,10 @@
         <v>19</v>
       </c>
       <c r="N31" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>1475</v>
       </c>
@@ -8413,10 +8411,10 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>1476</v>
       </c>
@@ -8457,10 +8455,10 @@
         <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1477</v>
       </c>
@@ -8489,10 +8487,10 @@
         <v>19</v>
       </c>
       <c r="N34" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>1478</v>
       </c>
@@ -8524,10 +8522,10 @@
         <v>19</v>
       </c>
       <c r="N35" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>1479</v>
       </c>
@@ -8565,10 +8563,10 @@
         <v>19</v>
       </c>
       <c r="N36" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>1480</v>
       </c>
@@ -8606,10 +8604,10 @@
         <v>19</v>
       </c>
       <c r="N37" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>1481</v>
       </c>
@@ -8650,10 +8648,10 @@
         <v>36</v>
       </c>
       <c r="N38" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>1482</v>
       </c>
@@ -8691,10 +8689,10 @@
         <v>19</v>
       </c>
       <c r="N39" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>1483</v>
       </c>
@@ -8732,10 +8730,10 @@
         <v>19</v>
       </c>
       <c r="N40" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>1484</v>
       </c>
@@ -8773,10 +8771,10 @@
         <v>19</v>
       </c>
       <c r="N41" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
         <v>2004</v>
@@ -8803,13 +8801,13 @@
         <v>35</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O42" s="4" t="s">
         <v>2020</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>1485</v>
       </c>
@@ -8838,10 +8836,10 @@
         <v>19</v>
       </c>
       <c r="N43" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>1486</v>
       </c>
@@ -8873,10 +8871,10 @@
         <v>19</v>
       </c>
       <c r="N44" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="15.75" thickBot="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>1487</v>
       </c>
@@ -8914,10 +8912,10 @@
         <v>19</v>
       </c>
       <c r="N45" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" s="4" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" s="4" customFormat="1" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>1488</v>
       </c>
@@ -8949,14 +8947,14 @@
         <v>142</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>2025</v>
       </c>
-      <c r="P46" s="6"/>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" thickTop="1">
+      <c r="P46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>1489</v>
       </c>
@@ -8985,10 +8983,10 @@
         <v>19</v>
       </c>
       <c r="N47" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>1490</v>
       </c>
@@ -9023,10 +9021,10 @@
         <v>19</v>
       </c>
       <c r="N48" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>1491</v>
       </c>
@@ -9055,13 +9053,13 @@
         <v>19</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O49" s="4" t="s">
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>1492</v>
       </c>
@@ -9093,10 +9091,10 @@
         <v>19</v>
       </c>
       <c r="N50" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>1493</v>
       </c>
@@ -9128,10 +9126,10 @@
         <v>19</v>
       </c>
       <c r="N51" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>1494</v>
       </c>
@@ -9169,10 +9167,10 @@
         <v>19</v>
       </c>
       <c r="N52" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>1495</v>
       </c>
@@ -9201,10 +9199,10 @@
         <v>19</v>
       </c>
       <c r="N53" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>1496</v>
       </c>
@@ -9236,13 +9234,13 @@
         <v>19</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>1497</v>
       </c>
@@ -9274,10 +9272,10 @@
         <v>19</v>
       </c>
       <c r="N55" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>1498</v>
       </c>
@@ -9309,10 +9307,10 @@
         <v>19</v>
       </c>
       <c r="N56" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>1499</v>
       </c>
@@ -9344,10 +9342,10 @@
         <v>19</v>
       </c>
       <c r="N57" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>1500</v>
       </c>
@@ -9379,10 +9377,10 @@
         <v>19</v>
       </c>
       <c r="N58" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>1501</v>
       </c>
@@ -9414,10 +9412,10 @@
         <v>19</v>
       </c>
       <c r="N59" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>1502</v>
       </c>
@@ -9449,10 +9447,10 @@
         <v>19</v>
       </c>
       <c r="N60" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>1503</v>
       </c>
@@ -9484,10 +9482,10 @@
         <v>19</v>
       </c>
       <c r="N61" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>1504</v>
       </c>
@@ -9516,10 +9514,10 @@
         <v>19</v>
       </c>
       <c r="N62" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>1505</v>
       </c>
@@ -9551,10 +9549,10 @@
         <v>19</v>
       </c>
       <c r="N63" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>1506</v>
       </c>
@@ -9586,10 +9584,10 @@
         <v>19</v>
       </c>
       <c r="N64" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>1507</v>
       </c>
@@ -9621,10 +9619,10 @@
         <v>19</v>
       </c>
       <c r="N65" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>1508</v>
       </c>
@@ -9653,10 +9651,10 @@
         <v>19</v>
       </c>
       <c r="N66" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>1509</v>
       </c>
@@ -9688,10 +9686,10 @@
         <v>19</v>
       </c>
       <c r="N67" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>1510</v>
       </c>
@@ -9720,10 +9718,10 @@
         <v>19</v>
       </c>
       <c r="N68" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>1511</v>
       </c>
@@ -9755,10 +9753,10 @@
         <v>19</v>
       </c>
       <c r="N69" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>1512</v>
       </c>
@@ -9790,10 +9788,10 @@
         <v>19</v>
       </c>
       <c r="N70" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>1513</v>
       </c>
@@ -9825,10 +9823,10 @@
         <v>19</v>
       </c>
       <c r="N71" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>1514</v>
       </c>
@@ -9866,10 +9864,10 @@
         <v>19</v>
       </c>
       <c r="N72" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>1515</v>
       </c>
@@ -9901,10 +9899,10 @@
         <v>19</v>
       </c>
       <c r="N73" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>1516</v>
       </c>
@@ -9936,10 +9934,10 @@
         <v>19</v>
       </c>
       <c r="N74" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>1517</v>
       </c>
@@ -9971,10 +9969,10 @@
         <v>19</v>
       </c>
       <c r="N75" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>1518</v>
       </c>
@@ -10006,10 +10004,10 @@
         <v>19</v>
       </c>
       <c r="N76" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>1519</v>
       </c>
@@ -10041,10 +10039,10 @@
         <v>19</v>
       </c>
       <c r="N77" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>1520</v>
       </c>
@@ -10076,10 +10074,10 @@
         <v>19</v>
       </c>
       <c r="N78" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>1521</v>
       </c>
@@ -10111,10 +10109,10 @@
         <v>19</v>
       </c>
       <c r="N79" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>1522</v>
       </c>
@@ -10143,10 +10141,10 @@
         <v>19</v>
       </c>
       <c r="N80" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>1523</v>
       </c>
@@ -10172,13 +10170,13 @@
         <v>35</v>
       </c>
       <c r="N81" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="4" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>230</v>
@@ -10208,13 +10206,13 @@
         <v>35</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>1524</v>
       </c>
@@ -10246,10 +10244,10 @@
         <v>19</v>
       </c>
       <c r="N83" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>1525</v>
       </c>
@@ -10281,10 +10279,10 @@
         <v>19</v>
       </c>
       <c r="N84" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>1526</v>
       </c>
@@ -10316,10 +10314,10 @@
         <v>19</v>
       </c>
       <c r="N85" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>1527</v>
       </c>
@@ -10351,10 +10349,10 @@
         <v>19</v>
       </c>
       <c r="N86" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>1528</v>
       </c>
@@ -10386,10 +10384,10 @@
         <v>19</v>
       </c>
       <c r="N87" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>1529</v>
       </c>
@@ -10421,10 +10419,10 @@
         <v>19</v>
       </c>
       <c r="N88" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>1530</v>
       </c>
@@ -10456,10 +10454,10 @@
         <v>19</v>
       </c>
       <c r="N89" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>1531</v>
       </c>
@@ -10491,10 +10489,10 @@
         <v>35</v>
       </c>
       <c r="N90" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>1532</v>
       </c>
@@ -10532,10 +10530,10 @@
         <v>19</v>
       </c>
       <c r="N91" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>1533</v>
       </c>
@@ -10567,10 +10565,10 @@
         <v>19</v>
       </c>
       <c r="N92" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>1534</v>
       </c>
@@ -10608,10 +10606,10 @@
         <v>19</v>
       </c>
       <c r="N93" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>1535</v>
       </c>
@@ -10634,10 +10632,10 @@
         <v>257</v>
       </c>
       <c r="N94" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>1536</v>
       </c>
@@ -10666,10 +10664,10 @@
         <v>19</v>
       </c>
       <c r="N95" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>1537</v>
       </c>
@@ -10698,10 +10696,10 @@
         <v>19</v>
       </c>
       <c r="N96" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>1538</v>
       </c>
@@ -10739,10 +10737,10 @@
         <v>19</v>
       </c>
       <c r="N97" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>1539</v>
       </c>
@@ -10780,10 +10778,10 @@
         <v>19</v>
       </c>
       <c r="N98" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>1540</v>
       </c>
@@ -10821,10 +10819,10 @@
         <v>274</v>
       </c>
       <c r="N99" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>1541</v>
       </c>
@@ -10862,10 +10860,10 @@
         <v>19</v>
       </c>
       <c r="N100" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>1542</v>
       </c>
@@ -10903,10 +10901,10 @@
         <v>274</v>
       </c>
       <c r="N101" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>1543</v>
       </c>
@@ -10944,10 +10942,10 @@
         <v>19</v>
       </c>
       <c r="N102" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>1544</v>
       </c>
@@ -10985,10 +10983,10 @@
         <v>19</v>
       </c>
       <c r="N103" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>1545</v>
       </c>
@@ -11026,10 +11024,10 @@
         <v>19</v>
       </c>
       <c r="N104" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>1546</v>
       </c>
@@ -11067,10 +11065,10 @@
         <v>19</v>
       </c>
       <c r="N105" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>1547</v>
       </c>
@@ -11108,13 +11106,13 @@
         <v>19</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O106" s="4" t="s">
         <v>2027</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>1548</v>
       </c>
@@ -11152,10 +11150,10 @@
         <v>19</v>
       </c>
       <c r="N107" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>1549</v>
       </c>
@@ -11193,10 +11191,10 @@
         <v>297</v>
       </c>
       <c r="N108" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>1550</v>
       </c>
@@ -11234,10 +11232,10 @@
         <v>297</v>
       </c>
       <c r="N109" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>1551</v>
       </c>
@@ -11275,10 +11273,10 @@
         <v>19</v>
       </c>
       <c r="N110" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="4" t="s">
         <v>2009</v>
@@ -11299,13 +11297,13 @@
         <v>2008</v>
       </c>
       <c r="N111" s="4" t="s">
-        <v>2046</v>
-      </c>
-      <c r="O111" s="5" t="s">
+        <v>2045</v>
+      </c>
+      <c r="O111" s="4" t="s">
         <v>2022</v>
       </c>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>1552</v>
       </c>
@@ -11343,10 +11341,10 @@
         <v>19</v>
       </c>
       <c r="N112" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>1553</v>
       </c>
@@ -11384,10 +11382,10 @@
         <v>19</v>
       </c>
       <c r="N113" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>1554</v>
       </c>
@@ -11416,10 +11414,10 @@
         <v>19</v>
       </c>
       <c r="N114" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>1555</v>
       </c>
@@ -11457,10 +11455,10 @@
         <v>19</v>
       </c>
       <c r="N115" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>1556</v>
       </c>
@@ -11498,10 +11496,10 @@
         <v>19</v>
       </c>
       <c r="N116" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>1557</v>
       </c>
@@ -11539,10 +11537,10 @@
         <v>19</v>
       </c>
       <c r="N117" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>1558</v>
       </c>
@@ -11580,10 +11578,10 @@
         <v>19</v>
       </c>
       <c r="N118" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>1559</v>
       </c>
@@ -11621,10 +11619,10 @@
         <v>19</v>
       </c>
       <c r="N119" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>1560</v>
       </c>
@@ -11662,10 +11660,10 @@
         <v>19</v>
       </c>
       <c r="N120" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>1561</v>
       </c>
@@ -11703,10 +11701,10 @@
         <v>19</v>
       </c>
       <c r="N121" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>1562</v>
       </c>
@@ -11744,10 +11742,10 @@
         <v>19</v>
       </c>
       <c r="N122" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>1563</v>
       </c>
@@ -11776,10 +11774,10 @@
         <v>19</v>
       </c>
       <c r="N123" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>1564</v>
       </c>
@@ -11817,10 +11815,10 @@
         <v>19</v>
       </c>
       <c r="N124" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>1565</v>
       </c>
@@ -11858,10 +11856,10 @@
         <v>19</v>
       </c>
       <c r="N125" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>1566</v>
       </c>
@@ -11899,10 +11897,10 @@
         <v>19</v>
       </c>
       <c r="N126" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>1567</v>
       </c>
@@ -11940,10 +11938,10 @@
         <v>19</v>
       </c>
       <c r="N127" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>1568</v>
       </c>
@@ -11981,10 +11979,10 @@
         <v>19</v>
       </c>
       <c r="N128" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>1569</v>
       </c>
@@ -12022,10 +12020,10 @@
         <v>19</v>
       </c>
       <c r="N129" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>1570</v>
       </c>
@@ -12063,10 +12061,10 @@
         <v>19</v>
       </c>
       <c r="N130" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>1571</v>
       </c>
@@ -12107,10 +12105,10 @@
         <v>364</v>
       </c>
       <c r="N131" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>1572</v>
       </c>
@@ -12139,10 +12137,10 @@
         <v>19</v>
       </c>
       <c r="N132" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>1573</v>
       </c>
@@ -12174,10 +12172,10 @@
         <v>19</v>
       </c>
       <c r="N133" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>1574</v>
       </c>
@@ -12215,10 +12213,10 @@
         <v>19</v>
       </c>
       <c r="N134" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>1575</v>
       </c>
@@ -12256,10 +12254,10 @@
         <v>19</v>
       </c>
       <c r="N135" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>1576</v>
       </c>
@@ -12297,10 +12295,10 @@
         <v>19</v>
       </c>
       <c r="N136" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>1577</v>
       </c>
@@ -12329,10 +12327,10 @@
         <v>19</v>
       </c>
       <c r="N137" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>1578</v>
       </c>
@@ -12361,10 +12359,10 @@
         <v>19</v>
       </c>
       <c r="N138" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>1579</v>
       </c>
@@ -12402,10 +12400,10 @@
         <v>19</v>
       </c>
       <c r="N139" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>1580</v>
       </c>
@@ -12443,10 +12441,10 @@
         <v>19</v>
       </c>
       <c r="N140" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>1581</v>
       </c>
@@ -12484,10 +12482,10 @@
         <v>19</v>
       </c>
       <c r="N141" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>1582</v>
       </c>
@@ -12525,10 +12523,10 @@
         <v>19</v>
       </c>
       <c r="N142" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>1583</v>
       </c>
@@ -12566,10 +12564,10 @@
         <v>19</v>
       </c>
       <c r="N143" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>1584</v>
       </c>
@@ -12607,10 +12605,10 @@
         <v>19</v>
       </c>
       <c r="N144" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>1585</v>
       </c>
@@ -12648,10 +12646,10 @@
         <v>19</v>
       </c>
       <c r="N145" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>1586</v>
       </c>
@@ -12683,10 +12681,10 @@
         <v>19</v>
       </c>
       <c r="N146" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>1587</v>
       </c>
@@ -12724,10 +12722,10 @@
         <v>19</v>
       </c>
       <c r="N147" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>1588</v>
       </c>
@@ -12765,10 +12763,10 @@
         <v>19</v>
       </c>
       <c r="N148" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="4" t="s">
         <v>1994</v>
@@ -12792,13 +12790,13 @@
         <v>35</v>
       </c>
       <c r="N149" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O149" s="4" t="s">
         <v>2016</v>
       </c>
     </row>
-    <row r="150" spans="1:15" s="4" customFormat="1">
+    <row r="150" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="4" t="s">
         <v>2000</v>
@@ -12822,13 +12820,13 @@
         <v>35</v>
       </c>
       <c r="N150" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O150" s="4" t="s">
         <v>2019</v>
       </c>
     </row>
-    <row r="151" spans="1:15" s="4" customFormat="1">
+    <row r="151" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="4" t="s">
         <v>2002</v>
@@ -12852,13 +12850,13 @@
         <v>35</v>
       </c>
       <c r="N151" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O151" s="4" t="s">
         <v>2019</v>
       </c>
     </row>
-    <row r="152" spans="1:15" s="4" customFormat="1">
+    <row r="152" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="4" t="s">
         <v>1998</v>
@@ -12882,16 +12880,16 @@
         <v>35</v>
       </c>
       <c r="N152" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O152" s="4" t="s">
         <v>2018</v>
       </c>
     </row>
-    <row r="153" spans="1:15" s="4" customFormat="1">
+    <row r="153" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="4" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>411</v>
@@ -12899,23 +12897,23 @@
       <c r="D153" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="E153" s="7">
+      <c r="E153" s="6">
         <v>38.408805999999998</v>
       </c>
-      <c r="F153" s="7">
+      <c r="F153" s="6">
         <v>-85.740795000000006</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="N153" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>1589</v>
       </c>
@@ -12953,10 +12951,10 @@
         <v>19</v>
       </c>
       <c r="N154" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>1590</v>
       </c>
@@ -12988,10 +12986,10 @@
         <v>19</v>
       </c>
       <c r="N155" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>1591</v>
       </c>
@@ -13023,10 +13021,10 @@
         <v>19</v>
       </c>
       <c r="N156" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>1592</v>
       </c>
@@ -13064,10 +13062,10 @@
         <v>19</v>
       </c>
       <c r="N157" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>1593</v>
       </c>
@@ -13099,10 +13097,10 @@
         <v>19</v>
       </c>
       <c r="N158" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>1594</v>
       </c>
@@ -13134,10 +13132,10 @@
         <v>19</v>
       </c>
       <c r="N159" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>1595</v>
       </c>
@@ -13169,10 +13167,10 @@
         <v>19</v>
       </c>
       <c r="N160" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>1596</v>
       </c>
@@ -13204,10 +13202,10 @@
         <v>19</v>
       </c>
       <c r="N161" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>1597</v>
       </c>
@@ -13245,13 +13243,13 @@
         <v>19</v>
       </c>
       <c r="N162" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O162" s="4" t="s">
         <v>2028</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>1598</v>
       </c>
@@ -13289,10 +13287,10 @@
         <v>19</v>
       </c>
       <c r="N163" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>1599</v>
       </c>
@@ -13330,10 +13328,10 @@
         <v>297</v>
       </c>
       <c r="N164" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>1600</v>
       </c>
@@ -13371,10 +13369,10 @@
         <v>19</v>
       </c>
       <c r="N165" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>1601</v>
       </c>
@@ -13412,10 +13410,10 @@
         <v>19</v>
       </c>
       <c r="N166" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>1602</v>
       </c>
@@ -13444,10 +13442,10 @@
         <v>19</v>
       </c>
       <c r="N167" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>1603</v>
       </c>
@@ -13476,10 +13474,10 @@
         <v>19</v>
       </c>
       <c r="N168" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>1604</v>
       </c>
@@ -13517,10 +13515,10 @@
         <v>19</v>
       </c>
       <c r="N169" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>1605</v>
       </c>
@@ -13549,10 +13547,10 @@
         <v>19</v>
       </c>
       <c r="N170" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>1606</v>
       </c>
@@ -13584,10 +13582,10 @@
         <v>19</v>
       </c>
       <c r="N171" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>1607</v>
       </c>
@@ -13625,10 +13623,10 @@
         <v>19</v>
       </c>
       <c r="N172" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>1608</v>
       </c>
@@ -13666,10 +13664,10 @@
         <v>19</v>
       </c>
       <c r="N173" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>1609</v>
       </c>
@@ -13701,10 +13699,10 @@
         <v>19</v>
       </c>
       <c r="N174" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>1610</v>
       </c>
@@ -13733,10 +13731,10 @@
         <v>19</v>
       </c>
       <c r="N175" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>1611</v>
       </c>
@@ -13774,10 +13772,10 @@
         <v>19</v>
       </c>
       <c r="N176" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>1612</v>
       </c>
@@ -13815,10 +13813,10 @@
         <v>19</v>
       </c>
       <c r="N177" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>1613</v>
       </c>
@@ -13856,10 +13854,10 @@
         <v>19</v>
       </c>
       <c r="N178" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>1614</v>
       </c>
@@ -13891,10 +13889,10 @@
         <v>19</v>
       </c>
       <c r="N179" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>1615</v>
       </c>
@@ -13932,10 +13930,10 @@
         <v>19</v>
       </c>
       <c r="N180" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>1616</v>
       </c>
@@ -13967,13 +13965,13 @@
         <v>19</v>
       </c>
       <c r="N181" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O181" s="4" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" s="4" customFormat="1">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>1617</v>
       </c>
@@ -14011,13 +14009,13 @@
         <v>19</v>
       </c>
       <c r="N182" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O182" s="4" t="s">
         <v>2029</v>
       </c>
     </row>
-    <row r="183" spans="1:15">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>1618</v>
       </c>
@@ -14049,10 +14047,10 @@
         <v>19</v>
       </c>
       <c r="N183" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>1619</v>
       </c>
@@ -14090,10 +14088,10 @@
         <v>19</v>
       </c>
       <c r="N184" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>1620</v>
       </c>
@@ -14125,10 +14123,10 @@
         <v>19</v>
       </c>
       <c r="N185" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>1621</v>
       </c>
@@ -14160,10 +14158,10 @@
         <v>19</v>
       </c>
       <c r="N186" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>1622</v>
       </c>
@@ -14195,10 +14193,10 @@
         <v>19</v>
       </c>
       <c r="N187" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>1623</v>
       </c>
@@ -14230,10 +14228,10 @@
         <v>19</v>
       </c>
       <c r="N188" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="189" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>1624</v>
       </c>
@@ -14262,10 +14260,10 @@
         <v>19</v>
       </c>
       <c r="N189" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="190" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>1625</v>
       </c>
@@ -14297,10 +14295,10 @@
         <v>19</v>
       </c>
       <c r="N190" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>1626</v>
       </c>
@@ -14332,10 +14330,10 @@
         <v>19</v>
       </c>
       <c r="N191" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>1627</v>
       </c>
@@ -14373,10 +14371,10 @@
         <v>19</v>
       </c>
       <c r="N192" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>1628</v>
       </c>
@@ -14408,10 +14406,10 @@
         <v>19</v>
       </c>
       <c r="N193" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>1629</v>
       </c>
@@ -14449,10 +14447,10 @@
         <v>19</v>
       </c>
       <c r="N194" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="195" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>1630</v>
       </c>
@@ -14490,10 +14488,10 @@
         <v>19</v>
       </c>
       <c r="N195" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="196" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>1631</v>
       </c>
@@ -14531,10 +14529,10 @@
         <v>19</v>
       </c>
       <c r="N196" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="197" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>1632</v>
       </c>
@@ -14563,10 +14561,10 @@
         <v>19</v>
       </c>
       <c r="N197" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="198" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>1633</v>
       </c>
@@ -14595,10 +14593,10 @@
         <v>19</v>
       </c>
       <c r="N198" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="199" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>1634</v>
       </c>
@@ -14627,10 +14625,10 @@
         <v>19</v>
       </c>
       <c r="N199" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>1635</v>
       </c>
@@ -14668,10 +14666,10 @@
         <v>19</v>
       </c>
       <c r="N200" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>1636</v>
       </c>
@@ -14700,10 +14698,10 @@
         <v>19</v>
       </c>
       <c r="N201" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>1637</v>
       </c>
@@ -14732,10 +14730,10 @@
         <v>19</v>
       </c>
       <c r="N202" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>1638</v>
       </c>
@@ -14764,10 +14762,10 @@
         <v>19</v>
       </c>
       <c r="N203" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>1639</v>
       </c>
@@ -14799,10 +14797,10 @@
         <v>19</v>
       </c>
       <c r="N204" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>1640</v>
       </c>
@@ -14831,10 +14829,10 @@
         <v>19</v>
       </c>
       <c r="N205" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>1641</v>
       </c>
@@ -14866,10 +14864,10 @@
         <v>19</v>
       </c>
       <c r="N206" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="207" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>1642</v>
       </c>
@@ -14898,10 +14896,10 @@
         <v>19</v>
       </c>
       <c r="N207" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>1643</v>
       </c>
@@ -14930,10 +14928,10 @@
         <v>19</v>
       </c>
       <c r="N208" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>1644</v>
       </c>
@@ -14962,10 +14960,10 @@
         <v>19</v>
       </c>
       <c r="N209" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>1645</v>
       </c>
@@ -15003,10 +15001,10 @@
         <v>19</v>
       </c>
       <c r="N210" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="211" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>1646</v>
       </c>
@@ -15044,10 +15042,10 @@
         <v>19</v>
       </c>
       <c r="N211" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="212" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>1647</v>
       </c>
@@ -15085,10 +15083,10 @@
         <v>19</v>
       </c>
       <c r="N212" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>1648</v>
       </c>
@@ -15126,10 +15124,10 @@
         <v>19</v>
       </c>
       <c r="N213" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="214" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>1649</v>
       </c>
@@ -15161,10 +15159,10 @@
         <v>19</v>
       </c>
       <c r="N214" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="215" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>1650</v>
       </c>
@@ -15193,10 +15191,10 @@
         <v>19</v>
       </c>
       <c r="N215" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="216" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>1651</v>
       </c>
@@ -15228,10 +15226,10 @@
         <v>19</v>
       </c>
       <c r="N216" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="217" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>1652</v>
       </c>
@@ -15260,10 +15258,10 @@
         <v>19</v>
       </c>
       <c r="N217" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="218" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>1653</v>
       </c>
@@ -15292,10 +15290,10 @@
         <v>19</v>
       </c>
       <c r="N218" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="219" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>1654</v>
       </c>
@@ -15327,10 +15325,10 @@
         <v>19</v>
       </c>
       <c r="N219" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>1655</v>
       </c>
@@ -15362,10 +15360,10 @@
         <v>19</v>
       </c>
       <c r="N220" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>1656</v>
       </c>
@@ -15397,10 +15395,10 @@
         <v>19</v>
       </c>
       <c r="N221" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="222" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>1657</v>
       </c>
@@ -15432,10 +15430,10 @@
         <v>19</v>
       </c>
       <c r="N222" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>1658</v>
       </c>
@@ -15467,10 +15465,10 @@
         <v>19</v>
       </c>
       <c r="N223" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>1659</v>
       </c>
@@ -15511,10 +15509,10 @@
         <v>603</v>
       </c>
       <c r="N224" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="225" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>1660</v>
       </c>
@@ -15546,10 +15544,10 @@
         <v>19</v>
       </c>
       <c r="N225" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="226" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>1661</v>
       </c>
@@ -15590,10 +15588,10 @@
         <v>603</v>
       </c>
       <c r="N226" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="227" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>1662</v>
       </c>
@@ -15631,10 +15629,10 @@
         <v>19</v>
       </c>
       <c r="N227" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="228" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>1663</v>
       </c>
@@ -15672,10 +15670,10 @@
         <v>19</v>
       </c>
       <c r="N228" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="229" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>1664</v>
       </c>
@@ -15713,10 +15711,10 @@
         <v>19</v>
       </c>
       <c r="N229" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>1665</v>
       </c>
@@ -15745,10 +15743,10 @@
         <v>19</v>
       </c>
       <c r="N230" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>1666</v>
       </c>
@@ -15780,10 +15778,10 @@
         <v>19</v>
       </c>
       <c r="N231" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>1667</v>
       </c>
@@ -15821,10 +15819,10 @@
         <v>19</v>
       </c>
       <c r="N232" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="233" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>1668</v>
       </c>
@@ -15853,10 +15851,10 @@
         <v>19</v>
       </c>
       <c r="N233" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="234" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>1669</v>
       </c>
@@ -15888,10 +15886,10 @@
         <v>19</v>
       </c>
       <c r="N234" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="235" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>1670</v>
       </c>
@@ -15929,10 +15927,10 @@
         <v>19</v>
       </c>
       <c r="N235" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="236" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>1671</v>
       </c>
@@ -15964,10 +15962,10 @@
         <v>19</v>
       </c>
       <c r="N236" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="237" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>1672</v>
       </c>
@@ -15996,13 +15994,13 @@
         <v>19</v>
       </c>
       <c r="N237" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="238" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3"/>
       <c r="B238" s="4" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>643</v>
@@ -16017,19 +16015,19 @@
         <v>-88.455856999999995</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="L238" s="4" t="s">
         <v>35</v>
       </c>
       <c r="N238" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O238" s="4" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="239" spans="1:15">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>1673</v>
       </c>
@@ -16064,10 +16062,10 @@
         <v>364</v>
       </c>
       <c r="N239" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="240" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>1674</v>
       </c>
@@ -16105,10 +16103,10 @@
         <v>19</v>
       </c>
       <c r="N240" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="241" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>1675</v>
       </c>
@@ -16146,10 +16144,10 @@
         <v>19</v>
       </c>
       <c r="N241" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="242" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>1676</v>
       </c>
@@ -16181,10 +16179,10 @@
         <v>19</v>
       </c>
       <c r="N242" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="243" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>1677</v>
       </c>
@@ -16219,10 +16217,10 @@
         <v>19</v>
       </c>
       <c r="N243" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="244" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>1678</v>
       </c>
@@ -16257,10 +16255,10 @@
         <v>659</v>
       </c>
       <c r="N244" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="245" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>1679</v>
       </c>
@@ -16295,10 +16293,10 @@
         <v>659</v>
       </c>
       <c r="N245" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="246" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>1680</v>
       </c>
@@ -16333,10 +16331,10 @@
         <v>364</v>
       </c>
       <c r="N246" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="247" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>1681</v>
       </c>
@@ -16374,10 +16372,10 @@
         <v>19</v>
       </c>
       <c r="N247" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="248" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>1682</v>
       </c>
@@ -16409,10 +16407,10 @@
         <v>19</v>
       </c>
       <c r="N248" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="249" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
       <c r="B249" s="4" t="s">
         <v>1996</v>
@@ -16433,13 +16431,13 @@
         <v>1997</v>
       </c>
       <c r="N249" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O249" s="4" t="s">
         <v>2017</v>
       </c>
     </row>
-    <row r="250" spans="1:15">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>1683</v>
       </c>
@@ -16477,10 +16475,10 @@
         <v>19</v>
       </c>
       <c r="N250" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="251" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>1684</v>
       </c>
@@ -16518,10 +16516,10 @@
         <v>19</v>
       </c>
       <c r="N251" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="252" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>1685</v>
       </c>
@@ -16550,10 +16548,10 @@
         <v>19</v>
       </c>
       <c r="N252" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="253" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>1686</v>
       </c>
@@ -16591,10 +16589,10 @@
         <v>19</v>
       </c>
       <c r="N253" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="254" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>1687</v>
       </c>
@@ -16617,10 +16615,10 @@
         <v>686</v>
       </c>
       <c r="N254" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="255" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>1688</v>
       </c>
@@ -16658,10 +16656,10 @@
         <v>19</v>
       </c>
       <c r="N255" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="256" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>1689</v>
       </c>
@@ -16690,10 +16688,10 @@
         <v>19</v>
       </c>
       <c r="N256" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="257" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>1690</v>
       </c>
@@ -16719,10 +16717,10 @@
         <v>35</v>
       </c>
       <c r="N257" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="258" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>1691</v>
       </c>
@@ -16754,10 +16752,10 @@
         <v>19</v>
       </c>
       <c r="N258" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="259" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>1692</v>
       </c>
@@ -16789,10 +16787,10 @@
         <v>19</v>
       </c>
       <c r="N259" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="260" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>1693</v>
       </c>
@@ -16821,10 +16819,10 @@
         <v>19</v>
       </c>
       <c r="N260" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="261" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>1694</v>
       </c>
@@ -16862,10 +16860,10 @@
         <v>19</v>
       </c>
       <c r="N261" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="262" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3"/>
       <c r="B262" s="4" t="s">
         <v>1991</v>
@@ -16886,13 +16884,13 @@
         <v>1993</v>
       </c>
       <c r="N262" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O262" s="4" t="s">
         <v>2015</v>
       </c>
     </row>
-    <row r="263" spans="1:15">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>1695</v>
       </c>
@@ -16921,10 +16919,10 @@
         <v>19</v>
       </c>
       <c r="N263" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="264" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>1696</v>
       </c>
@@ -16956,10 +16954,10 @@
         <v>19</v>
       </c>
       <c r="N264" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="265" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>1697</v>
       </c>
@@ -16991,10 +16989,10 @@
         <v>19</v>
       </c>
       <c r="N265" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="266" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>1698</v>
       </c>
@@ -17017,10 +17015,10 @@
         <v>720</v>
       </c>
       <c r="N266" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="267" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>1699</v>
       </c>
@@ -17061,10 +17059,10 @@
         <v>723</v>
       </c>
       <c r="N267" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="268" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>1700</v>
       </c>
@@ -17096,10 +17094,10 @@
         <v>19</v>
       </c>
       <c r="N268" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="269" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>1701</v>
       </c>
@@ -17128,10 +17126,10 @@
         <v>19</v>
       </c>
       <c r="N269" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="270" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>1702</v>
       </c>
@@ -17163,10 +17161,10 @@
         <v>19</v>
       </c>
       <c r="N270" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="271" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>1703</v>
       </c>
@@ -17195,10 +17193,10 @@
         <v>19</v>
       </c>
       <c r="N271" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="272" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>1704</v>
       </c>
@@ -17230,10 +17228,10 @@
         <v>19</v>
       </c>
       <c r="N272" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="273" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>1705</v>
       </c>
@@ -17265,10 +17263,10 @@
         <v>19</v>
       </c>
       <c r="N273" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="274" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>1706</v>
       </c>
@@ -17300,10 +17298,10 @@
         <v>19</v>
       </c>
       <c r="N274" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="275" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>1707</v>
       </c>
@@ -17335,10 +17333,10 @@
         <v>19</v>
       </c>
       <c r="N275" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>1708</v>
       </c>
@@ -17370,10 +17368,10 @@
         <v>19</v>
       </c>
       <c r="N276" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="277" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>1709</v>
       </c>
@@ -17405,10 +17403,10 @@
         <v>19</v>
       </c>
       <c r="N277" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="278" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>1710</v>
       </c>
@@ -17440,10 +17438,10 @@
         <v>19</v>
       </c>
       <c r="N278" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="279" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>1711</v>
       </c>
@@ -17484,10 +17482,10 @@
         <v>723</v>
       </c>
       <c r="N279" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="280" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3"/>
       <c r="B280" s="4" t="s">
         <v>2012</v>
@@ -17508,13 +17506,13 @@
         <v>2014</v>
       </c>
       <c r="N280" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O280" s="4" t="s">
         <v>2024</v>
       </c>
     </row>
-    <row r="281" spans="1:15">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>1712</v>
       </c>
@@ -17546,10 +17544,10 @@
         <v>19</v>
       </c>
       <c r="N281" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="282" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>1713</v>
       </c>
@@ -17578,10 +17576,10 @@
         <v>19</v>
       </c>
       <c r="N282" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="283" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>1714</v>
       </c>
@@ -17604,10 +17602,10 @@
         <v>720</v>
       </c>
       <c r="N283" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="284" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>1715</v>
       </c>
@@ -17636,10 +17634,10 @@
         <v>19</v>
       </c>
       <c r="N284" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="285" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>1716</v>
       </c>
@@ -17668,10 +17666,10 @@
         <v>19</v>
       </c>
       <c r="N285" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="286" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
         <v>1717</v>
       </c>
@@ -17703,13 +17701,13 @@
         <v>19</v>
       </c>
       <c r="N286" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O286" s="4" t="s">
         <v>2030</v>
       </c>
     </row>
-    <row r="287" spans="1:15">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>1718</v>
       </c>
@@ -17747,10 +17745,10 @@
         <v>19</v>
       </c>
       <c r="N287" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="288" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>1719</v>
       </c>
@@ -17788,10 +17786,10 @@
         <v>19</v>
       </c>
       <c r="N288" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="289" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>1720</v>
       </c>
@@ -17823,10 +17821,10 @@
         <v>19</v>
       </c>
       <c r="N289" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="290" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>1721</v>
       </c>
@@ -17858,10 +17856,10 @@
         <v>19</v>
       </c>
       <c r="N290" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="291" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>1722</v>
       </c>
@@ -17893,10 +17891,10 @@
         <v>19</v>
       </c>
       <c r="N291" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="292" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>1723</v>
       </c>
@@ -17925,10 +17923,10 @@
         <v>19</v>
       </c>
       <c r="N292" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="293" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>1724</v>
       </c>
@@ -17966,10 +17964,10 @@
         <v>19</v>
       </c>
       <c r="N293" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="294" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>1725</v>
       </c>
@@ -18007,10 +18005,10 @@
         <v>19</v>
       </c>
       <c r="N294" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="295" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>1726</v>
       </c>
@@ -18048,10 +18046,10 @@
         <v>19</v>
       </c>
       <c r="N295" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="296" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>1727</v>
       </c>
@@ -18089,10 +18087,10 @@
         <v>19</v>
       </c>
       <c r="N296" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="297" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>1728</v>
       </c>
@@ -18130,10 +18128,10 @@
         <v>19</v>
       </c>
       <c r="N297" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="298" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>1729</v>
       </c>
@@ -18171,10 +18169,10 @@
         <v>19</v>
       </c>
       <c r="N298" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="299" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>1730</v>
       </c>
@@ -18212,10 +18210,10 @@
         <v>19</v>
       </c>
       <c r="N299" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="300" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>1731</v>
       </c>
@@ -18253,10 +18251,10 @@
         <v>19</v>
       </c>
       <c r="N300" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="301" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>1732</v>
       </c>
@@ -18291,10 +18289,10 @@
         <v>804</v>
       </c>
       <c r="N301" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="302" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>1733</v>
       </c>
@@ -18326,10 +18324,10 @@
         <v>19</v>
       </c>
       <c r="N302" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="303" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>1734</v>
       </c>
@@ -18367,10 +18365,10 @@
         <v>19</v>
       </c>
       <c r="N303" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="304" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>1735</v>
       </c>
@@ -18408,10 +18406,10 @@
         <v>19</v>
       </c>
       <c r="N304" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="305" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>1736</v>
       </c>
@@ -18449,10 +18447,10 @@
         <v>19</v>
       </c>
       <c r="N305" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="306" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>1737</v>
       </c>
@@ -18490,10 +18488,10 @@
         <v>19</v>
       </c>
       <c r="N306" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="307" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>1738</v>
       </c>
@@ -18525,10 +18523,10 @@
         <v>19</v>
       </c>
       <c r="N307" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="308" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>1739</v>
       </c>
@@ -18557,10 +18555,10 @@
         <v>19</v>
       </c>
       <c r="N308" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="309" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>1740</v>
       </c>
@@ -18589,10 +18587,10 @@
         <v>19</v>
       </c>
       <c r="N309" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="310" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>1741</v>
       </c>
@@ -18621,10 +18619,10 @@
         <v>19</v>
       </c>
       <c r="N310" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="311" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>1742</v>
       </c>
@@ -18653,10 +18651,10 @@
         <v>19</v>
       </c>
       <c r="N311" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="312" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>1743</v>
       </c>
@@ -18694,10 +18692,10 @@
         <v>19</v>
       </c>
       <c r="N312" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="313" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>1744</v>
       </c>
@@ -18726,10 +18724,10 @@
         <v>19</v>
       </c>
       <c r="N313" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="314" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>1745</v>
       </c>
@@ -18758,10 +18756,10 @@
         <v>19</v>
       </c>
       <c r="N314" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="315" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>1746</v>
       </c>
@@ -18784,10 +18782,10 @@
         <v>835</v>
       </c>
       <c r="N315" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="316" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>1747</v>
       </c>
@@ -18810,10 +18808,10 @@
         <v>835</v>
       </c>
       <c r="N316" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="317" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>1748</v>
       </c>
@@ -18836,10 +18834,10 @@
         <v>835</v>
       </c>
       <c r="N317" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="318" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>1749</v>
       </c>
@@ -18862,10 +18860,10 @@
         <v>835</v>
       </c>
       <c r="N318" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="319" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>1750</v>
       </c>
@@ -18903,10 +18901,10 @@
         <v>19</v>
       </c>
       <c r="N319" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="320" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>1751</v>
       </c>
@@ -18944,10 +18942,10 @@
         <v>19</v>
       </c>
       <c r="N320" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="321" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>1752</v>
       </c>
@@ -18976,10 +18974,10 @@
         <v>19</v>
       </c>
       <c r="N321" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="322" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>1753</v>
       </c>
@@ -19017,10 +19015,10 @@
         <v>19</v>
       </c>
       <c r="N322" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="323" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>1754</v>
       </c>
@@ -19049,10 +19047,10 @@
         <v>19</v>
       </c>
       <c r="N323" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="324" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>1755</v>
       </c>
@@ -19090,10 +19088,10 @@
         <v>19</v>
       </c>
       <c r="N324" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="325" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>1756</v>
       </c>
@@ -19125,10 +19123,10 @@
         <v>19</v>
       </c>
       <c r="N325" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="326" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>1757</v>
       </c>
@@ -19160,10 +19158,10 @@
         <v>19</v>
       </c>
       <c r="N326" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="327" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>1758</v>
       </c>
@@ -19201,10 +19199,10 @@
         <v>19</v>
       </c>
       <c r="N327" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="328" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>1759</v>
       </c>
@@ -19242,10 +19240,10 @@
         <v>19</v>
       </c>
       <c r="N328" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="329" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>1760</v>
       </c>
@@ -19283,10 +19281,10 @@
         <v>19</v>
       </c>
       <c r="N329" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="330" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>1761</v>
       </c>
@@ -19324,10 +19322,10 @@
         <v>19</v>
       </c>
       <c r="N330" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="331" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>1762</v>
       </c>
@@ -19365,10 +19363,10 @@
         <v>19</v>
       </c>
       <c r="N331" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="332" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>1763</v>
       </c>
@@ -19406,10 +19404,10 @@
         <v>19</v>
       </c>
       <c r="N332" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="333" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>1764</v>
       </c>
@@ -19447,10 +19445,10 @@
         <v>19</v>
       </c>
       <c r="N333" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="334" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>1765</v>
       </c>
@@ -19488,10 +19486,10 @@
         <v>19</v>
       </c>
       <c r="N334" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="335" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>1766</v>
       </c>
@@ -19529,10 +19527,10 @@
         <v>19</v>
       </c>
       <c r="N335" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="336" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="336" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>1767</v>
       </c>
@@ -19570,13 +19568,13 @@
         <v>19</v>
       </c>
       <c r="N336" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O336" s="4" t="s">
         <v>2031</v>
       </c>
     </row>
-    <row r="337" spans="1:15">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>1768</v>
       </c>
@@ -19614,10 +19612,10 @@
         <v>19</v>
       </c>
       <c r="N337" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="338" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>1769</v>
       </c>
@@ -19655,10 +19653,10 @@
         <v>19</v>
       </c>
       <c r="N338" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="339" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>1770</v>
       </c>
@@ -19696,10 +19694,10 @@
         <v>19</v>
       </c>
       <c r="N339" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="340" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>1771</v>
       </c>
@@ -19737,10 +19735,10 @@
         <v>19</v>
       </c>
       <c r="N340" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="341" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>1772</v>
       </c>
@@ -19763,10 +19761,10 @@
         <v>900</v>
       </c>
       <c r="N341" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="342" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>1773</v>
       </c>
@@ -19795,10 +19793,10 @@
         <v>19</v>
       </c>
       <c r="N342" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="343" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>1774</v>
       </c>
@@ -19830,10 +19828,10 @@
         <v>19</v>
       </c>
       <c r="N343" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="344" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>1775</v>
       </c>
@@ -19862,10 +19860,10 @@
         <v>19</v>
       </c>
       <c r="N344" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="345" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>1776</v>
       </c>
@@ -19897,10 +19895,10 @@
         <v>19</v>
       </c>
       <c r="N345" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="346" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>1777</v>
       </c>
@@ -19938,10 +19936,10 @@
         <v>19</v>
       </c>
       <c r="N346" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="347" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>1778</v>
       </c>
@@ -19979,10 +19977,10 @@
         <v>19</v>
       </c>
       <c r="N347" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="348" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>1779</v>
       </c>
@@ -20014,10 +20012,10 @@
         <v>19</v>
       </c>
       <c r="N348" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="349" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>1780</v>
       </c>
@@ -20049,10 +20047,10 @@
         <v>19</v>
       </c>
       <c r="N349" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="350" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3"/>
       <c r="B350" s="4" t="s">
         <v>2010</v>
@@ -20073,13 +20071,13 @@
         <v>2011</v>
       </c>
       <c r="N350" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O350" s="4" t="s">
         <v>2023</v>
       </c>
     </row>
-    <row r="351" spans="1:15" s="4" customFormat="1" ht="14.65" customHeight="1">
+    <row r="351" spans="1:15" s="4" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3"/>
       <c r="B351" s="4" t="s">
         <v>1989</v>
@@ -20103,16 +20101,16 @@
         <v>35</v>
       </c>
       <c r="N351" s="4" t="s">
-        <v>2046</v>
-      </c>
-      <c r="O351" s="8" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="352" spans="1:15" s="4" customFormat="1">
+        <v>2045</v>
+      </c>
+      <c r="O351" s="4" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="352" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3"/>
       <c r="B352" s="4" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>922</v>
@@ -20127,16 +20125,16 @@
         <v>-79.708757000000006</v>
       </c>
       <c r="G352" s="4" t="s">
+        <v>2048</v>
+      </c>
+      <c r="N352" s="4" t="s">
+        <v>2045</v>
+      </c>
+      <c r="O352" s="4" t="s">
         <v>2049</v>
       </c>
-      <c r="N352" s="4" t="s">
-        <v>2046</v>
-      </c>
-      <c r="O352" s="4" t="s">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="353" spans="1:15" s="4" customFormat="1">
+    </row>
+    <row r="353" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3"/>
       <c r="B353" s="4" t="s">
         <v>2007</v>
@@ -20160,13 +20158,13 @@
         <v>35</v>
       </c>
       <c r="N353" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O353" s="4" t="s">
         <v>2021</v>
       </c>
     </row>
-    <row r="354" spans="1:15">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>1781</v>
       </c>
@@ -20198,10 +20196,10 @@
         <v>19</v>
       </c>
       <c r="N354" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="355" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>1782</v>
       </c>
@@ -20239,10 +20237,10 @@
         <v>19</v>
       </c>
       <c r="N355" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="356" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>1783</v>
       </c>
@@ -20274,10 +20272,10 @@
         <v>19</v>
       </c>
       <c r="N356" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="357" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="357" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
         <v>1784</v>
       </c>
@@ -20315,13 +20313,13 @@
         <v>19</v>
       </c>
       <c r="N357" s="4" t="s">
-        <v>2047</v>
-      </c>
-      <c r="O357" s="9" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="358" spans="1:15">
+        <v>2046</v>
+      </c>
+      <c r="O357" s="7" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>1785</v>
       </c>
@@ -20359,10 +20357,10 @@
         <v>19</v>
       </c>
       <c r="N358" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="359" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>1786</v>
       </c>
@@ -20400,10 +20398,10 @@
         <v>19</v>
       </c>
       <c r="N359" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="360" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>1787</v>
       </c>
@@ -20435,10 +20433,10 @@
         <v>19</v>
       </c>
       <c r="N360" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="361" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>1788</v>
       </c>
@@ -20467,10 +20465,10 @@
         <v>19</v>
       </c>
       <c r="N361" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="362" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>1789</v>
       </c>
@@ -20502,10 +20500,10 @@
         <v>19</v>
       </c>
       <c r="N362" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="363" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>1790</v>
       </c>
@@ -20546,10 +20544,10 @@
         <v>723</v>
       </c>
       <c r="N363" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="364" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>1791</v>
       </c>
@@ -20578,10 +20576,10 @@
         <v>19</v>
       </c>
       <c r="N364" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="365" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>1792</v>
       </c>
@@ -20610,10 +20608,10 @@
         <v>19</v>
       </c>
       <c r="N365" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="366" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>1793</v>
       </c>
@@ -20645,10 +20643,10 @@
         <v>19</v>
       </c>
       <c r="N366" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="367" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>1794</v>
       </c>
@@ -20680,10 +20678,10 @@
         <v>19</v>
       </c>
       <c r="N367" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="368" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>1795</v>
       </c>
@@ -20715,10 +20713,10 @@
         <v>19</v>
       </c>
       <c r="N368" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="369" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>1796</v>
       </c>
@@ -20756,10 +20754,10 @@
         <v>19</v>
       </c>
       <c r="N369" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="370" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>1797</v>
       </c>
@@ -20788,10 +20786,10 @@
         <v>19</v>
       </c>
       <c r="N370" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="371" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>1798</v>
       </c>
@@ -20823,10 +20821,10 @@
         <v>19</v>
       </c>
       <c r="N371" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="372" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>1799</v>
       </c>
@@ -20864,10 +20862,10 @@
         <v>19</v>
       </c>
       <c r="N372" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="373" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>1800</v>
       </c>
@@ -20905,10 +20903,10 @@
         <v>19</v>
       </c>
       <c r="N373" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="374" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20940,10 +20938,10 @@
         <v>19</v>
       </c>
       <c r="N374" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="375" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>1802</v>
       </c>
@@ -20981,10 +20979,10 @@
         <v>19</v>
       </c>
       <c r="N375" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="376" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>1803</v>
       </c>
@@ -21022,10 +21020,10 @@
         <v>19</v>
       </c>
       <c r="N376" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="377" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>1804</v>
       </c>
@@ -21057,10 +21055,10 @@
         <v>19</v>
       </c>
       <c r="N377" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="378" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>1805</v>
       </c>
@@ -21092,10 +21090,10 @@
         <v>19</v>
       </c>
       <c r="N378" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="379" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
         <v>1806</v>
       </c>
@@ -21133,10 +21131,10 @@
         <v>19</v>
       </c>
       <c r="N379" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="380" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>1807</v>
       </c>
@@ -21165,10 +21163,10 @@
         <v>19</v>
       </c>
       <c r="N380" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="381" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>1808</v>
       </c>
@@ -21206,10 +21204,10 @@
         <v>19</v>
       </c>
       <c r="N381" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="382" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>1809</v>
       </c>
@@ -21241,10 +21239,10 @@
         <v>19</v>
       </c>
       <c r="N382" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="383" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>1810</v>
       </c>
@@ -21282,10 +21280,10 @@
         <v>19</v>
       </c>
       <c r="N383" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="384" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>1811</v>
       </c>
@@ -21314,10 +21312,10 @@
         <v>19</v>
       </c>
       <c r="N384" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="385" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>1812</v>
       </c>
@@ -21346,10 +21344,10 @@
         <v>19</v>
       </c>
       <c r="N385" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="386" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>1813</v>
       </c>
@@ -21387,10 +21385,10 @@
         <v>19</v>
       </c>
       <c r="N386" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="387" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>1814</v>
       </c>
@@ -21419,10 +21417,10 @@
         <v>19</v>
       </c>
       <c r="N387" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="388" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>1815</v>
       </c>
@@ -21460,10 +21458,10 @@
         <v>19</v>
       </c>
       <c r="N388" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="389" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>1816</v>
       </c>
@@ -21495,10 +21493,10 @@
         <v>19</v>
       </c>
       <c r="N389" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="390" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>1817</v>
       </c>
@@ -21536,10 +21534,10 @@
         <v>19</v>
       </c>
       <c r="N390" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="391" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>1818</v>
       </c>
@@ -21571,10 +21569,10 @@
         <v>19</v>
       </c>
       <c r="N391" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="392" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>1819</v>
       </c>
@@ -21612,10 +21610,10 @@
         <v>19</v>
       </c>
       <c r="N392" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="393" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>1820</v>
       </c>
@@ -21647,10 +21645,10 @@
         <v>19</v>
       </c>
       <c r="N393" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="394" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>1821</v>
       </c>
@@ -21682,10 +21680,10 @@
         <v>19</v>
       </c>
       <c r="N394" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="395" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>1822</v>
       </c>
@@ -21723,10 +21721,10 @@
         <v>19</v>
       </c>
       <c r="N395" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="396" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>1823</v>
       </c>
@@ -21764,10 +21762,10 @@
         <v>19</v>
       </c>
       <c r="N396" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="397" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>1824</v>
       </c>
@@ -21799,10 +21797,10 @@
         <v>19</v>
       </c>
       <c r="N397" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="398" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>1825</v>
       </c>
@@ -21834,10 +21832,10 @@
         <v>19</v>
       </c>
       <c r="N398" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="399" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>1826</v>
       </c>
@@ -21869,10 +21867,10 @@
         <v>19</v>
       </c>
       <c r="N399" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="400" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>1827</v>
       </c>
@@ -21904,10 +21902,10 @@
         <v>19</v>
       </c>
       <c r="N400" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="401" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>1828</v>
       </c>
@@ -21939,10 +21937,10 @@
         <v>19</v>
       </c>
       <c r="N401" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="402" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>1829</v>
       </c>
@@ -21974,10 +21972,10 @@
         <v>19</v>
       </c>
       <c r="N402" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="403" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>1830</v>
       </c>
@@ -22006,10 +22004,10 @@
         <v>19</v>
       </c>
       <c r="N403" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="404" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>1831</v>
       </c>
@@ -22047,10 +22045,10 @@
         <v>19</v>
       </c>
       <c r="N404" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="405" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>1832</v>
       </c>
@@ -22088,10 +22086,10 @@
         <v>19</v>
       </c>
       <c r="N405" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="406" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>1833</v>
       </c>
@@ -22123,10 +22121,10 @@
         <v>19</v>
       </c>
       <c r="N406" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="407" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>1834</v>
       </c>
@@ -22164,10 +22162,10 @@
         <v>19</v>
       </c>
       <c r="N407" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="408" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>1835</v>
       </c>
@@ -22196,10 +22194,10 @@
         <v>19</v>
       </c>
       <c r="N408" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="409" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="409" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
         <v>1836</v>
       </c>
@@ -22231,13 +22229,13 @@
         <v>19</v>
       </c>
       <c r="N409" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O409" s="4" t="s">
         <v>2032</v>
       </c>
     </row>
-    <row r="410" spans="1:15">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
         <v>1837</v>
       </c>
@@ -22269,10 +22267,10 @@
         <v>19</v>
       </c>
       <c r="N410" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="411" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="411" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
         <v>1838</v>
       </c>
@@ -22310,13 +22308,13 @@
         <v>19</v>
       </c>
       <c r="N411" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O411" s="4" t="s">
         <v>2033</v>
       </c>
     </row>
-    <row r="412" spans="1:15">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>1839</v>
       </c>
@@ -22354,10 +22352,10 @@
         <v>19</v>
       </c>
       <c r="N412" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="413" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>1840</v>
       </c>
@@ -22395,10 +22393,10 @@
         <v>19</v>
       </c>
       <c r="N413" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="414" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>1841</v>
       </c>
@@ -22430,10 +22428,10 @@
         <v>19</v>
       </c>
       <c r="N414" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="415" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>1842</v>
       </c>
@@ -22471,10 +22469,10 @@
         <v>19</v>
       </c>
       <c r="N415" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="416" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>1843</v>
       </c>
@@ -22506,10 +22504,10 @@
         <v>19</v>
       </c>
       <c r="N416" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="417" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>1844</v>
       </c>
@@ -22538,10 +22536,10 @@
         <v>19</v>
       </c>
       <c r="N417" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="418" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>1845</v>
       </c>
@@ -22570,10 +22568,10 @@
         <v>19</v>
       </c>
       <c r="N418" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="419" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>1846</v>
       </c>
@@ -22602,10 +22600,10 @@
         <v>19</v>
       </c>
       <c r="N419" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="420" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>1847</v>
       </c>
@@ -22634,10 +22632,10 @@
         <v>19</v>
       </c>
       <c r="N420" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="421" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>1848</v>
       </c>
@@ -22675,10 +22673,10 @@
         <v>19</v>
       </c>
       <c r="N421" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="422" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
         <v>1849</v>
       </c>
@@ -22716,10 +22714,10 @@
         <v>19</v>
       </c>
       <c r="N422" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="423" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>1850</v>
       </c>
@@ -22754,10 +22752,10 @@
         <v>19</v>
       </c>
       <c r="N423" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="424" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>1851</v>
       </c>
@@ -22792,10 +22790,10 @@
         <v>19</v>
       </c>
       <c r="N424" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="425" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
         <v>1852</v>
       </c>
@@ -22833,10 +22831,10 @@
         <v>19</v>
       </c>
       <c r="N425" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="426" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
         <v>1853</v>
       </c>
@@ -22874,10 +22872,10 @@
         <v>19</v>
       </c>
       <c r="N426" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="427" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
         <v>1854</v>
       </c>
@@ -22912,10 +22910,10 @@
         <v>19</v>
       </c>
       <c r="N427" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="428" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
         <v>1855</v>
       </c>
@@ -22953,10 +22951,10 @@
         <v>19</v>
       </c>
       <c r="N428" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="429" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
         <v>1856</v>
       </c>
@@ -22994,10 +22992,10 @@
         <v>19</v>
       </c>
       <c r="N429" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="430" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
         <v>1857</v>
       </c>
@@ -23035,10 +23033,10 @@
         <v>19</v>
       </c>
       <c r="N430" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="431" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
         <v>1858</v>
       </c>
@@ -23076,10 +23074,10 @@
         <v>19</v>
       </c>
       <c r="N431" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="432" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
         <v>1859</v>
       </c>
@@ -23117,10 +23115,10 @@
         <v>19</v>
       </c>
       <c r="N432" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="433" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="433" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
         <v>1860</v>
       </c>
@@ -23149,13 +23147,13 @@
         <v>19</v>
       </c>
       <c r="N433" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O433" s="4" t="s">
         <v>2034</v>
       </c>
     </row>
-    <row r="434" spans="1:15">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
         <v>1861</v>
       </c>
@@ -23187,10 +23185,10 @@
         <v>19</v>
       </c>
       <c r="N434" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="435" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
         <v>1862</v>
       </c>
@@ -23222,10 +23220,10 @@
         <v>35</v>
       </c>
       <c r="N435" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="436" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
         <v>1863</v>
       </c>
@@ -23257,10 +23255,10 @@
         <v>35</v>
       </c>
       <c r="N436" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="437" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
         <v>1864</v>
       </c>
@@ -23292,10 +23290,10 @@
         <v>19</v>
       </c>
       <c r="N437" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="438" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
         <v>1865</v>
       </c>
@@ -23327,10 +23325,10 @@
         <v>19</v>
       </c>
       <c r="N438" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="439" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="439" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
         <v>1866</v>
       </c>
@@ -23368,10 +23366,10 @@
         <v>19</v>
       </c>
       <c r="N439" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="440" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="440" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
         <v>1867</v>
       </c>
@@ -23409,10 +23407,10 @@
         <v>19</v>
       </c>
       <c r="N440" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="441" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
         <v>1868</v>
       </c>
@@ -23441,10 +23439,10 @@
         <v>19</v>
       </c>
       <c r="N441" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="442" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="442" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
         <v>1869</v>
       </c>
@@ -23476,10 +23474,10 @@
         <v>19</v>
       </c>
       <c r="N442" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="443" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="443" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
         <v>1870</v>
       </c>
@@ -23517,13 +23515,13 @@
         <v>19</v>
       </c>
       <c r="N443" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O443" s="4" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="444" spans="1:15">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="444" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
         <v>1871</v>
       </c>
@@ -23561,10 +23559,10 @@
         <v>19</v>
       </c>
       <c r="N444" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="445" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="445" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
         <v>1872</v>
       </c>
@@ -23602,10 +23600,10 @@
         <v>19</v>
       </c>
       <c r="N445" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="446" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="446" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
         <v>1873</v>
       </c>
@@ -23643,10 +23641,10 @@
         <v>19</v>
       </c>
       <c r="N446" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="447" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="447" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
         <v>1874</v>
       </c>
@@ -23684,10 +23682,10 @@
         <v>19</v>
       </c>
       <c r="N447" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="448" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="448" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
         <v>1875</v>
       </c>
@@ -23725,10 +23723,10 @@
         <v>19</v>
       </c>
       <c r="N448" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="449" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
         <v>1876</v>
       </c>
@@ -23766,10 +23764,10 @@
         <v>19</v>
       </c>
       <c r="N449" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="450" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
         <v>1877</v>
       </c>
@@ -23807,10 +23805,10 @@
         <v>19</v>
       </c>
       <c r="N450" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="451" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
         <v>1878</v>
       </c>
@@ -23848,13 +23846,13 @@
         <v>19</v>
       </c>
       <c r="N451" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="452" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="452" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3"/>
       <c r="B452" s="4" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>1163</v>
@@ -23866,16 +23864,16 @@
         <v>-84.308008000000001</v>
       </c>
       <c r="G452" s="4" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="N452" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O452" s="4" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="453" spans="1:15">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
         <v>1879</v>
       </c>
@@ -23907,10 +23905,10 @@
         <v>19</v>
       </c>
       <c r="N453" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="454" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
         <v>1880</v>
       </c>
@@ -23942,10 +23940,10 @@
         <v>19</v>
       </c>
       <c r="N454" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="455" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
         <v>1881</v>
       </c>
@@ -23983,10 +23981,10 @@
         <v>19</v>
       </c>
       <c r="N455" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="456" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
         <v>1882</v>
       </c>
@@ -24024,10 +24022,10 @@
         <v>19</v>
       </c>
       <c r="N456" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="457" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
         <v>1883</v>
       </c>
@@ -24059,10 +24057,10 @@
         <v>19</v>
       </c>
       <c r="N457" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="458" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="458" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
         <v>1884</v>
       </c>
@@ -24094,13 +24092,13 @@
         <v>19</v>
       </c>
       <c r="N458" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O458" s="4" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="459" spans="1:15">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
         <v>1885</v>
       </c>
@@ -24129,10 +24127,10 @@
         <v>19</v>
       </c>
       <c r="N459" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="460" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
         <v>1886</v>
       </c>
@@ -24164,10 +24162,10 @@
         <v>19</v>
       </c>
       <c r="N460" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="461" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>1887</v>
       </c>
@@ -24199,10 +24197,10 @@
         <v>19</v>
       </c>
       <c r="N461" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="462" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>1888</v>
       </c>
@@ -24234,10 +24232,10 @@
         <v>19</v>
       </c>
       <c r="N462" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="463" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>1889</v>
       </c>
@@ -24269,10 +24267,10 @@
         <v>19</v>
       </c>
       <c r="N463" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="464" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
         <v>1890</v>
       </c>
@@ -24304,10 +24302,10 @@
         <v>19</v>
       </c>
       <c r="N464" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="465" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>1891</v>
       </c>
@@ -24339,10 +24337,10 @@
         <v>19</v>
       </c>
       <c r="N465" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="466" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>1892</v>
       </c>
@@ -24374,10 +24372,10 @@
         <v>19</v>
       </c>
       <c r="N466" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="467" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>1893</v>
       </c>
@@ -24409,10 +24407,10 @@
         <v>19</v>
       </c>
       <c r="N467" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="468" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>1894</v>
       </c>
@@ -24444,10 +24442,10 @@
         <v>19</v>
       </c>
       <c r="N468" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="469" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
         <v>1895</v>
       </c>
@@ -24479,10 +24477,10 @@
         <v>19</v>
       </c>
       <c r="N469" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="470" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
         <v>1896</v>
       </c>
@@ -24520,13 +24518,13 @@
         <v>19</v>
       </c>
       <c r="N470" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="471" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="471" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3"/>
       <c r="B471" s="4" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="C471" s="4" t="s">
         <v>1206</v>
@@ -24541,16 +24539,16 @@
         <v>-78.502921999999998</v>
       </c>
       <c r="N471" s="4" t="s">
-        <v>2046</v>
-      </c>
-      <c r="O471" s="10" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="472" spans="1:15" s="4" customFormat="1">
+        <v>2045</v>
+      </c>
+      <c r="O471" s="8" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="472" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3"/>
       <c r="B472" s="4" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>1206</v>
@@ -24562,13 +24560,13 @@
         <v>-82.191188999999994</v>
       </c>
       <c r="N472" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O472" s="4" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="473" spans="1:15">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
         <v>1897</v>
       </c>
@@ -24594,10 +24592,10 @@
         <v>35</v>
       </c>
       <c r="N473" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="474" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>1898</v>
       </c>
@@ -24626,10 +24624,10 @@
         <v>19</v>
       </c>
       <c r="N474" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="475" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="475" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
         <v>1899</v>
       </c>
@@ -24658,10 +24656,10 @@
         <v>19</v>
       </c>
       <c r="N475" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="476" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="476" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
         <v>1900</v>
       </c>
@@ -24693,10 +24691,10 @@
         <v>19</v>
       </c>
       <c r="N476" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="477" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A477" s="2" t="s">
         <v>1901</v>
       </c>
@@ -24728,10 +24726,10 @@
         <v>19</v>
       </c>
       <c r="N477" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="478" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="478" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A478" s="2" t="s">
         <v>1902</v>
       </c>
@@ -24763,10 +24761,10 @@
         <v>19</v>
       </c>
       <c r="N478" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="479" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="479" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A479" s="2" t="s">
         <v>1903</v>
       </c>
@@ -24798,10 +24796,10 @@
         <v>19</v>
       </c>
       <c r="N479" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="480" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="480" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
         <v>1904</v>
       </c>
@@ -24833,10 +24831,10 @@
         <v>19</v>
       </c>
       <c r="N480" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="481" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="481" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
         <v>1905</v>
       </c>
@@ -24874,10 +24872,10 @@
         <v>19</v>
       </c>
       <c r="N481" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="482" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="482" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
         <v>1906</v>
       </c>
@@ -24915,10 +24913,10 @@
         <v>19</v>
       </c>
       <c r="N482" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="483" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
         <v>1907</v>
       </c>
@@ -24956,10 +24954,10 @@
         <v>19</v>
       </c>
       <c r="N483" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="484" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="484" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
         <v>1908</v>
       </c>
@@ -24997,10 +24995,10 @@
         <v>19</v>
       </c>
       <c r="N484" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="485" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="485" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
         <v>1909</v>
       </c>
@@ -25023,10 +25021,10 @@
         <v>1238</v>
       </c>
       <c r="N485" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="486" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
         <v>1910</v>
       </c>
@@ -25064,10 +25062,10 @@
         <v>19</v>
       </c>
       <c r="N486" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="487" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
         <v>1911</v>
       </c>
@@ -25096,10 +25094,10 @@
         <v>19</v>
       </c>
       <c r="N487" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="488" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
         <v>1912</v>
       </c>
@@ -25131,10 +25129,10 @@
         <v>19</v>
       </c>
       <c r="N488" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="489" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="489" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
         <v>1913</v>
       </c>
@@ -25163,10 +25161,10 @@
         <v>19</v>
       </c>
       <c r="N489" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="490" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A490" s="2" t="s">
         <v>1914</v>
       </c>
@@ -25198,10 +25196,10 @@
         <v>19</v>
       </c>
       <c r="N490" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="491" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A491" s="2" t="s">
         <v>1915</v>
       </c>
@@ -25239,10 +25237,10 @@
         <v>19</v>
       </c>
       <c r="N491" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="492" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A492" s="2" t="s">
         <v>1916</v>
       </c>
@@ -25274,10 +25272,10 @@
         <v>19</v>
       </c>
       <c r="N492" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="493" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
         <v>1917</v>
       </c>
@@ -25306,10 +25304,10 @@
         <v>19</v>
       </c>
       <c r="N493" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="494" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
         <v>1918</v>
       </c>
@@ -25347,10 +25345,10 @@
         <v>19</v>
       </c>
       <c r="N494" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="495" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A495" s="2" t="s">
         <v>1919</v>
       </c>
@@ -25382,10 +25380,10 @@
         <v>19</v>
       </c>
       <c r="N495" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="496" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A496" s="2" t="s">
         <v>1920</v>
       </c>
@@ -25423,10 +25421,10 @@
         <v>19</v>
       </c>
       <c r="N496" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="497" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="497" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
         <v>1921</v>
       </c>
@@ -25464,10 +25462,10 @@
         <v>19</v>
       </c>
       <c r="N497" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="498" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="498" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
         <v>1922</v>
       </c>
@@ -25499,10 +25497,10 @@
         <v>19</v>
       </c>
       <c r="N498" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="499" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="499" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
         <v>1923</v>
       </c>
@@ -25534,10 +25532,10 @@
         <v>19</v>
       </c>
       <c r="N499" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="500" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="500" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
         <v>1924</v>
       </c>
@@ -25566,10 +25564,10 @@
         <v>19</v>
       </c>
       <c r="N500" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="501" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="501" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
         <v>1925</v>
       </c>
@@ -25607,10 +25605,10 @@
         <v>19</v>
       </c>
       <c r="N501" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="502" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="502" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A502" s="2" t="s">
         <v>1926</v>
       </c>
@@ -25648,10 +25646,10 @@
         <v>19</v>
       </c>
       <c r="N502" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="503" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="503" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A503" s="2" t="s">
         <v>1927</v>
       </c>
@@ -25683,10 +25681,10 @@
         <v>19</v>
       </c>
       <c r="N503" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="504" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="504" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A504" s="2" t="s">
         <v>1928</v>
       </c>
@@ -25718,10 +25716,10 @@
         <v>19</v>
       </c>
       <c r="N504" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="505" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="505" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
         <v>1929</v>
       </c>
@@ -25753,10 +25751,10 @@
         <v>19</v>
       </c>
       <c r="N505" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="506" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A506" s="3" t="s">
         <v>1930</v>
       </c>
@@ -25785,13 +25783,13 @@
         <v>35</v>
       </c>
       <c r="N506" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O506" s="4" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="507" spans="1:15">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="507" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A507" s="2" t="s">
         <v>1931</v>
       </c>
@@ -25829,10 +25827,10 @@
         <v>19</v>
       </c>
       <c r="N507" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="508" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="508" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A508" s="2" t="s">
         <v>1932</v>
       </c>
@@ -25861,10 +25859,10 @@
         <v>19</v>
       </c>
       <c r="N508" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="509" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="509" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
         <v>1933</v>
       </c>
@@ -25902,10 +25900,10 @@
         <v>19</v>
       </c>
       <c r="N509" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="510" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="510" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
         <v>1934</v>
       </c>
@@ -25943,10 +25941,10 @@
         <v>19</v>
       </c>
       <c r="N510" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="511" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="511" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
         <v>1935</v>
       </c>
@@ -25984,10 +25982,10 @@
         <v>19</v>
       </c>
       <c r="N511" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="512" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="512" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A512" s="2" t="s">
         <v>1936</v>
       </c>
@@ -26025,10 +26023,10 @@
         <v>19</v>
       </c>
       <c r="N512" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="513" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
         <v>1937</v>
       </c>
@@ -26066,10 +26064,10 @@
         <v>19</v>
       </c>
       <c r="N513" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="514" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="514" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
         <v>1938</v>
       </c>
@@ -26098,10 +26096,10 @@
         <v>19</v>
       </c>
       <c r="N514" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="515" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
         <v>1939</v>
       </c>
@@ -26130,13 +26128,13 @@
         <v>19</v>
       </c>
       <c r="N515" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O515" s="4" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="516" spans="1:15">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
         <v>1940</v>
       </c>
@@ -26168,10 +26166,10 @@
         <v>19</v>
       </c>
       <c r="N516" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="517" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="517" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A517" s="2" t="s">
         <v>1941</v>
       </c>
@@ -26209,10 +26207,10 @@
         <v>19</v>
       </c>
       <c r="N517" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="518" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A518" s="2" t="s">
         <v>1942</v>
       </c>
@@ -26244,10 +26242,10 @@
         <v>19</v>
       </c>
       <c r="N518" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="519" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A519" s="2" t="s">
         <v>1943</v>
       </c>
@@ -26279,10 +26277,10 @@
         <v>19</v>
       </c>
       <c r="N519" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="520" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A520" s="2" t="s">
         <v>1944</v>
       </c>
@@ -26320,10 +26318,10 @@
         <v>19</v>
       </c>
       <c r="N520" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="521" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="521" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A521" s="2" t="s">
         <v>1945</v>
       </c>
@@ -26355,10 +26353,10 @@
         <v>19</v>
       </c>
       <c r="N521" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="522" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="522" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A522" s="2" t="s">
         <v>1946</v>
       </c>
@@ -26387,10 +26385,10 @@
         <v>19</v>
       </c>
       <c r="N522" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="523" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="523" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A523" s="2" t="s">
         <v>1947</v>
       </c>
@@ -26422,10 +26420,10 @@
         <v>19</v>
       </c>
       <c r="N523" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="524" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A524" s="2" t="s">
         <v>1948</v>
       </c>
@@ -26454,10 +26452,10 @@
         <v>19</v>
       </c>
       <c r="N524" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="525" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="525" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A525" s="2" t="s">
         <v>1949</v>
       </c>
@@ -26495,10 +26493,10 @@
         <v>19</v>
       </c>
       <c r="N525" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="526" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A526" s="2" t="s">
         <v>1950</v>
       </c>
@@ -26536,10 +26534,10 @@
         <v>19</v>
       </c>
       <c r="N526" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="527" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
         <v>1951</v>
       </c>
@@ -26574,10 +26572,10 @@
         <v>19</v>
       </c>
       <c r="N527" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="528" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="528" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
         <v>1952</v>
       </c>
@@ -26606,10 +26604,10 @@
         <v>19</v>
       </c>
       <c r="N528" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="529" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="529" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A529" s="2" t="s">
         <v>1953</v>
       </c>
@@ -26638,10 +26636,10 @@
         <v>19</v>
       </c>
       <c r="N529" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="530" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="530" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
         <v>1954</v>
       </c>
@@ -26676,10 +26674,10 @@
         <v>19</v>
       </c>
       <c r="N530" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="531" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="531" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A531" s="2" t="s">
         <v>1955</v>
       </c>
@@ -26717,10 +26715,10 @@
         <v>19</v>
       </c>
       <c r="N531" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="532" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="532" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
         <v>1956</v>
       </c>
@@ -26758,10 +26756,10 @@
         <v>19</v>
       </c>
       <c r="N532" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="533" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="533" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A533" s="2" t="s">
         <v>1957</v>
       </c>
@@ -26799,10 +26797,10 @@
         <v>19</v>
       </c>
       <c r="N533" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="534" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="534" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A534" s="2" t="s">
         <v>1958</v>
       </c>
@@ -26840,10 +26838,10 @@
         <v>19</v>
       </c>
       <c r="N534" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="535" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="535" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A535" s="2" t="s">
         <v>1959</v>
       </c>
@@ -26881,10 +26879,10 @@
         <v>19</v>
       </c>
       <c r="N535" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="536" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="536" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A536" s="2" t="s">
         <v>1960</v>
       </c>
@@ -26922,10 +26920,10 @@
         <v>19</v>
       </c>
       <c r="N536" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="537" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="537" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
         <v>1961</v>
       </c>
@@ -26963,13 +26961,13 @@
         <v>19</v>
       </c>
       <c r="N537" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O537" s="4" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="538" spans="1:15">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="538" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A538" s="2" t="s">
         <v>1962</v>
       </c>
@@ -27007,10 +27005,10 @@
         <v>19</v>
       </c>
       <c r="N538" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="539" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="539" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
         <v>1963</v>
       </c>
@@ -27048,10 +27046,10 @@
         <v>19</v>
       </c>
       <c r="N539" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="540" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="540" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
         <v>1964</v>
       </c>
@@ -27080,10 +27078,10 @@
         <v>19</v>
       </c>
       <c r="N540" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="541" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="541" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A541" s="2" t="s">
         <v>1965</v>
       </c>
@@ -27112,10 +27110,10 @@
         <v>19</v>
       </c>
       <c r="N541" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="542" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="542" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A542" s="2" t="s">
         <v>1966</v>
       </c>
@@ -27144,10 +27142,10 @@
         <v>19</v>
       </c>
       <c r="N542" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="543" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="543" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A543" s="2" t="s">
         <v>1967</v>
       </c>
@@ -27176,10 +27174,10 @@
         <v>19</v>
       </c>
       <c r="N543" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="544" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="544" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A544" s="2" t="s">
         <v>1968</v>
       </c>
@@ -27208,10 +27206,10 @@
         <v>19</v>
       </c>
       <c r="N544" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="545" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="545" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A545" s="2" t="s">
         <v>1969</v>
       </c>
@@ -27243,10 +27241,10 @@
         <v>19</v>
       </c>
       <c r="N545" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="546" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="546" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A546" s="2" t="s">
         <v>1970</v>
       </c>
@@ -27284,10 +27282,10 @@
         <v>19</v>
       </c>
       <c r="N546" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="547" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="547" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A547" s="2" t="s">
         <v>1971</v>
       </c>
@@ -27319,10 +27317,10 @@
         <v>19</v>
       </c>
       <c r="N547" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="548" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="548" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
         <v>1972</v>
       </c>
@@ -27354,10 +27352,10 @@
         <v>19</v>
       </c>
       <c r="N548" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="549" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="549" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A549" s="2" t="s">
         <v>1973</v>
       </c>
@@ -27389,10 +27387,10 @@
         <v>19</v>
       </c>
       <c r="N549" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="550" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="550" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A550" s="2" t="s">
         <v>1974</v>
       </c>
@@ -27424,10 +27422,10 @@
         <v>19</v>
       </c>
       <c r="N550" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="551" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="551" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A551" s="2" t="s">
         <v>1975</v>
       </c>
@@ -27459,10 +27457,10 @@
         <v>19</v>
       </c>
       <c r="N551" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="552" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="552" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A552" s="2" t="s">
         <v>1976</v>
       </c>
@@ -27494,10 +27492,10 @@
         <v>19</v>
       </c>
       <c r="N552" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="553" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="553" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A553" s="2" t="s">
         <v>1977</v>
       </c>
@@ -27529,10 +27527,10 @@
         <v>19</v>
       </c>
       <c r="N553" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="554" spans="1:15" s="4" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="554" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A554" s="3" t="s">
         <v>1978</v>
       </c>
@@ -27561,13 +27559,13 @@
         <v>19</v>
       </c>
       <c r="N554" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O554" s="4" t="s">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="555" spans="1:15">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="555" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
         <v>1979</v>
       </c>
@@ -27599,10 +27597,10 @@
         <v>19</v>
       </c>
       <c r="N555" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="556" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="556" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
         <v>1980</v>
       </c>
@@ -27634,10 +27632,10 @@
         <v>19</v>
       </c>
       <c r="N556" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="557" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="557" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A557" s="2" t="s">
         <v>1981</v>
       </c>
@@ -27669,10 +27667,10 @@
         <v>19</v>
       </c>
       <c r="N557" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="558" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="558" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A558" s="2" t="s">
         <v>1982</v>
       </c>
@@ -27710,10 +27708,10 @@
         <v>19</v>
       </c>
       <c r="N558" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="559" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="559" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A559" s="2" t="s">
         <v>1983</v>
       </c>
@@ -27751,10 +27749,10 @@
         <v>19</v>
       </c>
       <c r="N559" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="560" spans="1:15">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="560" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A560" s="2" t="s">
         <v>1984</v>
       </c>
@@ -27792,10 +27790,10 @@
         <v>19</v>
       </c>
       <c r="N560" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="561" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="561" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A561" s="2" t="s">
         <v>1985</v>
       </c>
@@ -27824,10 +27822,10 @@
         <v>19</v>
       </c>
       <c r="N561" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="562" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="562" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A562" s="2" t="s">
         <v>1986</v>
       </c>
@@ -27865,10 +27863,10 @@
         <v>19</v>
       </c>
       <c r="N562" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="563" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="563" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A563" s="2" t="s">
         <v>1987</v>
       </c>
@@ -27906,10 +27904,10 @@
         <v>19</v>
       </c>
       <c r="N563" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="564" spans="1:14">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="564" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A564" s="2" t="s">
         <v>1988</v>
       </c>
@@ -27947,7 +27945,7 @@
         <v>19</v>
       </c>
       <c r="N564" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
     </row>
   </sheetData>
